--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
@@ -177,18 +177,18 @@
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
     <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recoleta</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tiltil</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:53</t>
+    <t xml:space="preserve">2026-09-10 01:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1426,7 +1426,7 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13101</v>
+        <v>13127</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -1439,7 +1439,7 @@
         <v>54</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>13106</v>
+        <v>13125</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -1452,7 +1452,7 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>13125</v>
+        <v>13101</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -1465,7 +1465,7 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13127</v>
+        <v>13106</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:04</t>
+    <t xml:space="preserve">2026-09-18 11:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
@@ -174,21 +174,21 @@
     <t xml:space="preserve">Vitacura</t>
   </si>
   <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estación Central</t>
+  </si>
+  <si>
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recoleta</t>
   </si>
   <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estación Central</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tiltil</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:11</t>
+    <t xml:space="preserve">2026-09-23 14:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1413,9 +1413,11 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13108</v>
-      </c>
-      <c r="D48" s="2"/>
+        <v>13101</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
@@ -1426,9 +1428,11 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13127</v>
-      </c>
-      <c r="D49" s="2"/>
+        <v>13106</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
@@ -1439,9 +1443,11 @@
         <v>54</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>13125</v>
-      </c>
-      <c r="D50" s="2"/>
+        <v>13108</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
@@ -1452,9 +1458,11 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>13101</v>
-      </c>
-      <c r="D51" s="2"/>
+        <v>13125</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
@@ -1465,9 +1473,11 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13106</v>
-      </c>
-      <c r="D52" s="2"/>
+        <v>13127</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
@@ -1480,7 +1490,9 @@
       <c r="C53" s="2" t="n">
         <v>13303</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:35</t>
+    <t xml:space="preserve">2026-10-02 15:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:50</t>
+    <t xml:space="preserve">2026-10-05 15:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
